--- a/output/roomself_excel/2559.xlsx
+++ b/output/roomself_excel/2559.xlsx
@@ -498,10 +498,10 @@
         <v>8776</v>
       </c>
       <c r="E3" t="n">
-        <v>967</v>
+        <v>908</v>
       </c>
       <c r="F3" t="n">
-        <v>908</v>
+        <v>631</v>
       </c>
     </row>
     <row r="4">
@@ -520,10 +520,10 @@
         <v>1584</v>
       </c>
       <c r="E4" t="n">
-        <v>537</v>
+        <v>218</v>
       </c>
       <c r="F4" t="n">
-        <v>218</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -542,7 +542,7 @@
         <v>1268</v>
       </c>
       <c r="E5" t="n">
-        <v>537</v>
+        <v>212</v>
       </c>
       <c r="F5" t="n">
         <v>173</v>
@@ -586,10 +586,10 @@
         <v>1808</v>
       </c>
       <c r="E7" t="n">
-        <v>547</v>
+        <v>161</v>
       </c>
       <c r="F7" t="n">
-        <v>312</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -608,7 +608,7 @@
         <v>1740</v>
       </c>
       <c r="E8" t="n">
-        <v>537</v>
+        <v>306</v>
       </c>
       <c r="F8" t="n">
         <v>205</v>
@@ -630,10 +630,10 @@
         <v>2228</v>
       </c>
       <c r="E9" t="n">
-        <v>479</v>
+        <v>335</v>
       </c>
       <c r="F9" t="n">
-        <v>335</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">

--- a/output/roomself_excel/2559.xlsx
+++ b/output/roomself_excel/2559.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2684</v>
       </c>
-      <c r="E2" t="n">
-        <v>413</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>324</v>
+        <v>292</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>379</v>
+      </c>
+      <c r="J2" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>8776</v>
       </c>
-      <c r="E3" t="n">
-        <v>908</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>631</v>
+        <v>1186</v>
+      </c>
+      <c r="G3" t="n">
+        <v>34</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>337</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +571,20 @@
       <c r="D4" t="n">
         <v>1584</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>218</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>34</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +601,27 @@
       <c r="D5" t="n">
         <v>1268</v>
       </c>
-      <c r="E5" t="n">
-        <v>212</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>173</v>
+        <v>139</v>
+      </c>
+      <c r="G5" t="n">
+        <v>34</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>178</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +639,20 @@
       <c r="D6" t="n">
         <v>1252</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>108</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>10</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +669,20 @@
       <c r="D7" t="n">
         <v>1808</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>161</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>44</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +699,27 @@
       <c r="D8" t="n">
         <v>1740</v>
       </c>
-      <c r="E8" t="n">
-        <v>306</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>205</v>
+        <v>268</v>
+      </c>
+      <c r="G8" t="n">
+        <v>38</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>167</v>
+      </c>
+      <c r="J8" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -629,12 +737,20 @@
       <c r="D9" t="n">
         <v>2228</v>
       </c>
-      <c r="E9" t="n">
-        <v>335</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>265</v>
       </c>
+      <c r="G9" t="n">
+        <v>32</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +767,27 @@
       <c r="D10" t="n">
         <v>1084</v>
       </c>
-      <c r="E10" t="n">
-        <v>203</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>134</v>
+        <v>169</v>
+      </c>
+      <c r="G10" t="n">
+        <v>32</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>102</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -673,12 +805,20 @@
       <c r="D11" t="n">
         <v>1396</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>180</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>34</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/2559.xlsx
+++ b/output/roomself_excel/2559.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,86 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +597,46 @@
       <c r="J2" t="n">
         <v>32</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>118</v>
+      </c>
+      <c r="N2" t="n">
+        <v>34</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>86</v>
+      </c>
+      <c r="R2" t="n">
+        <v>32</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -555,6 +675,70 @@
       <c r="J3" t="n">
         <v>34</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>664</v>
+      </c>
+      <c r="N3" t="n">
+        <v>34</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>82</v>
+      </c>
+      <c r="R3" t="n">
+        <v>34</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>153</v>
+      </c>
+      <c r="V3" t="n">
+        <v>34</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>114</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -585,6 +769,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>96</v>
+      </c>
+      <c r="N4" t="n">
+        <v>34</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -623,6 +835,34 @@
       <c r="J5" t="n">
         <v>34</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>83</v>
+      </c>
+      <c r="N5" t="n">
+        <v>34</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -653,6 +893,22 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -683,6 +939,34 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>58</v>
+      </c>
+      <c r="N7" t="n">
+        <v>44</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -721,6 +1005,34 @@
       <c r="J8" t="n">
         <v>38</v>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>116</v>
+      </c>
+      <c r="N8" t="n">
+        <v>38</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -751,6 +1063,34 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>87</v>
+      </c>
+      <c r="N9" t="n">
+        <v>32</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -789,6 +1129,34 @@
       <c r="J10" t="n">
         <v>34</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>83</v>
+      </c>
+      <c r="N10" t="n">
+        <v>34</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -819,6 +1187,34 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>92</v>
+      </c>
+      <c r="N11" t="n">
+        <v>34</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
